--- a/packets_export.xlsx
+++ b/packets_export.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,23 +500,23 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-11 18:07:59</t>
+          <t>2025-10-15 13:07:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>b'\x01\xaa3\x0cgt\x85\xda\xd2\xea\x8b\x07\xc2\xdf\x00\x00\xc1(\x00\x00C\x8d\x08\x92\x00\x00\x00\x00'</t>
+          <t>b'\x01U3\x0cgt\x86i|e\xcc\xdb\xc2X\x00\x00A$\x00\x00\xc4\xe7\x9a\xae'</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>51</v>
@@ -525,47 +525,47 @@
         <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>1735689690</v>
+        <v>1735689833</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3538586375</t>
+          <t>2087046363</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-70</v>
+        <v>-50</v>
       </c>
       <c r="K2" t="n">
-        <v>10.1</v>
+        <v>10.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1848.64</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dati telemetria</t>
+          <t>test</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-11 18:08:47</t>
+          <t>2025-10-15 13:21:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>b'\x01\xaa3\x0cgt\x85\xda\xd2\xea\x8b\x07\xc2\xdf\x00\x00\xc1(\x00\x00C\x8d\x08\x92\x00\x00\x00\x00'</t>
+          <t>b'\x01U3\x0cgt\x89\xc7\x11\xdb\xb7\xb1\xc2X\x00\x00A$\x00\x00\xc4\x97 C'</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>51</v>
@@ -574,172 +574,460 @@
         <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>1735689690</v>
+        <v>1735690695</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3538586375</t>
+          <t>299612081</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-70</v>
+        <v>-50</v>
       </c>
       <c r="K3" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1202.72</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dati telemetria</t>
+          <t>test3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-11 18:12:09</t>
+          <t>2025-10-15 13:23:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>b'\x01\xaa3\x0cgt\x85\xda\xd2\xea\x8b\x07\xc2\xdf\x00\x00\xc1(\x00\x00C\x8d\x08\x92\x00\x00\x00\x00'</t>
+          <t>b'\x01U1\x01gt\x8a,\x03\xfbz_\x18'</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1735689690</v>
+        <v>1735690796</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3538586375</t>
+          <t>66812511</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-70</v>
+        <v>-54</v>
       </c>
       <c r="K4" t="n">
-        <v>10.1</v>
+        <v>9.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1274.02</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dati telemetria</t>
+          <t>test4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-11 18:18:08</t>
+          <t>2025-10-15 13:23:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>b'\x01\xaa3\x0cgt\x85\xda\xd2\xea\x8b\x07\xc2\xdf\x00\x00\xc1(\x00\x00C\x8d\x08\x92\x00\x00\x00\x00'</t>
+          <t>b'\x01U1\x01gt\x8a1\x9a\x02\xf4\xa5\x18'</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1735689690</v>
+        <v>1735690801</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3538586375</t>
+          <t>2583884965</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-70</v>
+        <v>-54</v>
       </c>
       <c r="K5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1204.81</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dati telemetria</t>
+          <t>test4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-11 18:20:40</t>
+          <t>2025-10-15 13:26:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>b'\x01\xaa3\x0cgt\x85\xda\xd2\xea\x8b\x07\xc2\xdf\x00\x00\xc1(\x00\x00C\x8d\x08\x92\x00\x00\x00\x00'</t>
+          <t>b'\x01U1\x01gt\x8a\xd1;K\xfd\x8c\x18'</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1735690961</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>994835852</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>-53</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>298.84</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>test5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:26:26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>b'\x01U1\x01gt\x8a\xd6/ew\x87\x18'</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1735690966</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>795178887</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>-54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>test5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:28:54</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>b'\x01U1\x01gt\x8bk\x96\xe2\x03u\x18'</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1735691115</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2531394421</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>-54</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>714.08</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>test8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:28:59</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>b'\x01U1\x01gt\x8bpO\xc4\xae\xeb\x18'</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1735691120</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1338289899</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>-53</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="L9" t="n">
+        <v>691.01</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>test8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:49:01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0cgt\x90!\xed\xfc\xa7s\xc2\\\x00\x00A,\x00\x00\xc4\xf4/\xe8'</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>51</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G10" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
-        <v>1735689690</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3538586375</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>-70</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="H10" t="n">
+        <v>1735692321</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3992758131</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>-49</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1945.11</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>qwe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:50:42</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>b'\x10U\x1a\x00h\xef\xa6\xad\xfaX\x9cQ'</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Dati telemetria</t>
+      <c r="F11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1760536237</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4200111185</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:50:43</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0cgt\x90\x87\xc8\n\xe7\xd2\xc2\\\x00\x00A,\x00\x00\xc4\xf2\x9dA'</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>51</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1735692423</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3356157906</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>-50</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1934.62</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -754,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -847,6 +1135,62 @@
       </c>
       <c r="D6" t="n">
         <v>282.0669555664062</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-54</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1852.833740234375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-54</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1209.008178710938</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1953.4970703125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-55</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1940.914184570312</v>
       </c>
     </row>
   </sheetData>
@@ -891,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +1250,58 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/packets_export.xlsx
+++ b/packets_export.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,7 +439,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>GS_time</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>unix</t>
+          <t>TX_time</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -500,16 +500,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-10-15 13:07:33</t>
+          <t>2025-10-15 22:16:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>b'\x01U3\x0cgt\x86i|e\xcc\xdb\xc2X\x00\x00A$\x00\x00\xc4\xe7\x9a\xae'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xdd\xf4d\x89\x8f\xc2\x92\x00\x00AX\x00\x00D\xb0\x8d\xd2'</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -524,41 +524,43 @@
       <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
-        <v>1735689833</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:25</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2087046363</t>
+          <t>4100229519</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-50</v>
+        <v>-63</v>
       </c>
       <c r="K2" t="n">
-        <v>10.75</v>
+        <v>12.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1848.64</v>
+        <v>-1414.53</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-10-15 13:21:55</t>
+          <t>2025-10-15 22:16:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>b'\x01U3\x0cgt\x89\xc7\x11\xdb\xb7\xb1\xc2X\x00\x00A$\x00\x00\xc4\x97 C'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xe0B\xdf\x1a\xa7\xc2\x92\x00\x00A\\\x00\x00D\xb0\x8d\xd2'</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -573,41 +575,43 @@
       <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
-        <v>1735690695</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:28</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>299612081</t>
+          <t>1121917607</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-50</v>
+        <v>-63</v>
       </c>
       <c r="K3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1202.72</v>
+        <v>-1416.63</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>test3</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-10-15 13:23:36</t>
+          <t>2025-10-15 22:16:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>b'\x01U1\x01gt\x8a,\x03\xfbz_\x18'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xe2\x9e3\xef\xf4\xc2\x94\x00\x00A\\\x00\x00D\xb0\xd0\xee'</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -617,46 +621,48 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1735690796</v>
+        <v>12</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:30</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>66812511</t>
+          <t>2654203892</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-54</v>
+        <v>-64</v>
       </c>
       <c r="K4" t="n">
-        <v>9.75</v>
+        <v>12.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1274.02</v>
+        <v>-1420.82</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-15 13:23:41</t>
+          <t>2025-10-15 22:16:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>b'\x01U1\x01gt\x8a1\x9a\x02\xf4\xa5\x18'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xe4\xa5h\x06\x1a\xc2\x92\x00\x00AP\x00\x00D\xb0\xd0\xee'</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -666,46 +672,48 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1735690801</v>
+        <v>12</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:32</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2583884965</t>
+          <t>2775057946</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-54</v>
+        <v>-64</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>12.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1204.81</v>
+        <v>-1418.72</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-10-15 13:26:21</t>
+          <t>2025-10-15 22:16:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>b'\x01U1\x01gt\x8a\xd1;K\xfd\x8c\x18'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xe6\x9ff\x0cp\xc2\x94\x00\x00AX\x00\x00D\xb0\xd0\xee'</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -715,46 +723,48 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1735690961</v>
+        <v>12</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:34</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>994835852</t>
+          <t>2674265200</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-53</v>
+        <v>-63</v>
       </c>
       <c r="K6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
-        <v>298.84</v>
+        <v>-1422.92</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-10-15 13:26:26</t>
+          <t>2025-10-15 22:16:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>b'\x01U1\x01gt\x8a\xd6/ew\x87\x18'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xe8J\xbc\xf6\xf6\xc2\x92\x00\x00A\\\x00\x00D\xb0\xd0\xee'</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -764,46 +774,48 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1735690966</v>
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:36</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>795178887</t>
+          <t>1253897974</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-54</v>
+        <v>-64</v>
       </c>
       <c r="K7" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>246.42</v>
+        <v>-1416.63</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-10-15 13:28:54</t>
+          <t>2025-10-15 22:16:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>b'\x01U1\x01gt\x8bk\x96\xe2\x03u\x18'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xea\xad\xa7\x1d\x14\xc2\x92\x00\x00AX\x00\x00D\xb0\x8d\xd2'</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -813,46 +825,48 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1735691115</v>
+        <v>12</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:38</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2531394421</t>
+          <t>2913410324</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-54</v>
+        <v>-63</v>
       </c>
       <c r="K8" t="n">
-        <v>10.25</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>714.08</v>
+        <v>-1416.63</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>test8</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-10-15 13:28:59</t>
+          <t>2025-10-15 22:16:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>b'\x01U1\x01gt\x8bpO\xc4\xae\xeb\x18'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xec\xeb\x7f~\x8e\xc2\x92\x00\x00AX\x00\x00D\xb0\x8d\xd2'</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -862,46 +876,48 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1735691120</v>
+        <v>12</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:40</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1338289899</t>
+          <t>3951001230</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-53</v>
+        <v>-63</v>
       </c>
       <c r="K9" t="n">
-        <v>10.25</v>
+        <v>12.5</v>
       </c>
       <c r="L9" t="n">
-        <v>691.01</v>
+        <v>-1416.63</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>test8</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-10-15 15:49:01</t>
+          <t>2025-10-15 22:16:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b'\x01U3\x0cgt\x90!\xed\xfc\xa7s\xc2\\\x00\x00A,\x00\x00\xc4\xf4/\xe8'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xee\xe6\xba\x99\xf5\xc2\x92\x00\x00AL\x00\x00D\xb0J\xb6'</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -916,118 +932,4159 @@
       <c r="G10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" t="n">
-        <v>1735692321</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:42</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3992758131</t>
+          <t>3870988789</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-49</v>
+        <v>-64</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>12.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1945.11</v>
+        <v>-1414.53</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>qwe</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10-15 15:50:42</t>
+          <t>2025-10-15 22:16:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>b'\x10U\x1a\x00h\xef\xa6\xad\xfaX\x9cQ'</t>
+          <t>b'\x01U3\x0ch\xf0\x00\xf0\xa9\x95\x82\xaa\xc2\x92\x00\x00AX\x00\x00D\xb0\x07\x9a'</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1760536237</v>
+        <v>12</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:44</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4200111185</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>2845147818</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>-63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1414.53</v>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>histo</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:43</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x00\xf3Q\x82\xe1G\xc2\x92\x00\x00AX\x00\x00D\xb0\x07\x9a'</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>51</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:47</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1367531847</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>-63</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1412.43</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x00\xf5\xb8D\xf3K\xc2\x94\x00\x00A,\x00\x00D\xaf\xc4~'</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>51</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:49</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3091526475</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1410.33</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:48</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x00\xf7=K\x0c\r\xc2\x98\x00\x00A0\x00\x00D\xb0\x07\x9a'</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:51</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1028328461</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1412.43</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:49</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x00\xf9\x8d\xeb\xb7]\xc2\x90\x00\x00AD\x00\x00D\xaf\xc4~'</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>51</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:53</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2381035357</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1410.33</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:52</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x00\xfb\xeb\xf5vb\xc2\x98\x00\x00A4\x00\x00D\xaf\xc4~'</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>51</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:55</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3958732386</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>-70</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1410.33</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2025-10-15 15:50:43</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0cgt\x90\x87\xc8\n\xe7\xd2\xc2\\\x00\x00A,\x00\x00\xc4\xf2\x9dA'</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>51</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1735692423</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3356157906</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>-50</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1934.62</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>a</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:54</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x00\xfe\xc6M\xe4x\xc2\x9a\x00\x00A$\x00\x00D\xaf\xc4~'</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:15:58</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3326993528</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K17" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1410.33</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:57</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x00\xcfz\xde\xfe\xc2\x9e\x00\x00AT\x00\x00D\xaf\xc4~'</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>51</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3480936190</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>-69</v>
+      </c>
+      <c r="K18" t="n">
+        <v>12</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1410.33</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:16:59</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x02W\x05\xf1T\xc2\x9a\x00\x00A4\x00\x00D\xaf&gt;G'</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:02</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1460007252</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1408.24</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\t\x06Cm\xdd\xc2\x9e\x00\x00AL\x00\x00D\xaf\x81b'</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>51</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:09</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105082333</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1408.24</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x0b\x9e\x8a\xb02\xc2\x9c\x00\x00AP\x00\x00D\xaf&gt;G'</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>51</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:11</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2659889202</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1406.14</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\r\xe7\xcd\xc74\xc2\x98\x00\x00A\x18\x00\x00D\xae\xfb+'</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:13</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3889022772</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1408.24</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x0f~#\xfbh\xc2\x98\x00\x00A\x1c\x00\x00D\xaf&gt;G'</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>51</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:15</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2116287336</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1406.14</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x11\xbf\x8f\x90\x9a\xc2\x98\x00\x00A$\x00\x00D\xaf\x81b'</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>51</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:17</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3213856922</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1408.24</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x13\xeb\x96Cp\xc2\x98\x00\x00A$\x00\x00D\xaf&gt;G'</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>51</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:19</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3952493424</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1406.14</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:18</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x16^\xeb\xdc\xca\xc2\x9a\x00\x00A \x00\x00D\xaf&gt;G'</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>51</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:22</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1592515786</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1406.14</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x17\x00\xb3\xaa\x0e\xc2\x9a\x00\x00A \x00\x00D\xae\xfb+'</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>51</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:23</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11774478</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1404.04</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:22</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x1aWP\t;\xc2\x9a\x00\x00A$\x00\x00D\xae\xfb+'</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>51</v>
+      </c>
+      <c r="G28" t="n">
+        <v>12</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:26</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1464863035</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K28" t="n">
+        <v>11</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1404.04</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x1cvS\xe7f\xc2\x98\x00\x00A(\x00\x00D\xae\xb8\x0f'</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>51</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:28</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1985210214</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1401.95</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x1e\xf2,\x93\x05\xc2\x96\x00\x00A$\x00\x00D\xae\xb8\x0f'</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>51</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:30</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4063007493</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-1401.95</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01 |a\xf0@\xc2\x9a\x00\x00A\x1c\x00\x00D\xae\xb8\x0f'</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>51</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:32</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2086793280</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1401.95</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01"i&amp;3y\xc2\x98\x00\x00A\x14\x00\x00D\xaet\xf3'</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>51</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:34</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1764111225</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K32" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-1399.85</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:33</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01%\xbat)\x0f\xc2\x9a\x00\x00A\x14\x00\x00D\xaet\xf3'</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>51</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:37</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3128174863</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K33" t="n">
+        <v>11</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-1399.85</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:35</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>b"\x01U3\x0ch\xf0\x01'}\x80d\x9d\xc2\x98\x00\x00A,\x00\x00D\xaet\xf3"</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>51</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:39</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2105566365</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K34" t="n">
+        <v>11</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1401.95</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:38</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01)\xeb\x9a!\xe1\xc2\x98\x00\x00A$\x00\x00D\xaet\xf3'</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>51</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:41</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3952746977</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K35" t="n">
+        <v>11</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-1399.85</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:39</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01+\xcb[\x14\x16\xc2\x9a\x00\x00A\x18\x00\x00D\xaet\xf3'</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>51</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:43</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3411743766</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K36" t="n">
+        <v>11</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-1399.85</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:42</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01-\xddVf\x97\xc2\x98\x00\x00A(\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>51</v>
+      </c>
+      <c r="G37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:45</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3713427095</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K37" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-1399.85</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:44</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01/\xf7\xab{S\xc2\x9a\x00\x00A,\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>51</v>
+      </c>
+      <c r="G38" t="n">
+        <v>12</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:47</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4155210579</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K38" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-1397.75</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:47</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x012\x13k;\xf9\xc2\x9a\x00\x00A\x10\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>51</v>
+      </c>
+      <c r="G39" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:50</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>325794809</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-1397.75</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:49</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>b"\x01U3\x0ch\xf0\x014:\xe6'H\xc2\x9a\x00\x00A$\x00\x00D\xae1\xd7"</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>51</v>
+      </c>
+      <c r="G40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:52</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>988161864</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K40" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:51</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x017\xce&gt;U\xeb\xc2\x9a\x00\x00A\x1c\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>51</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:55</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3460191723</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-1397.75</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:54</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x019\x80L\xea?\xc2\x98\x00\x00A$\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51</v>
+      </c>
+      <c r="G42" t="n">
+        <v>12</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:16:57</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2152524351</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K42" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-1397.75</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:56</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01&lt;\xe1\xfb\x0e\xf8\xc2\x9c\x00\x00A4\x00\x00D\xaet\xf3'</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>51</v>
+      </c>
+      <c r="G43" t="n">
+        <v>12</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3791326968</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:17:59</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01&gt;\x85XI\xa9\xc2\x96\x00\x00A4\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>51</v>
+      </c>
+      <c r="G44" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:02</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2237155753</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>-63</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01@d\xf2\x06\xc6\xc2\xa0\x00\x00A&lt;\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51</v>
+      </c>
+      <c r="G45" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:04</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1693583046</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K45" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:03</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01C\x00i\x80\xec\xc2\x9a\x00\x00A(\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>51</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:07</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6914284</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K46" t="n">
+        <v>11</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01EVa\x06\xc0\xc2\x9a\x00\x00A\x1c\x00\x00D\xae1\xd7'</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>51</v>
+      </c>
+      <c r="G47" t="n">
+        <v>12</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:09</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1449199296</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K47" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:07</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01GW\x9d\xc2\x9d\xc2\x9a\x00\x00A\x1c\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>51</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:11</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1469956765</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K48" t="n">
+        <v>11</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:09</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01IpI\x11\x89\xc2\x9a\x00\x00A\x18\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>51</v>
+      </c>
+      <c r="G49" t="n">
+        <v>12</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:13</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1883836809</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K49" t="n">
+        <v>7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-1355.81</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:12</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01Ku\xf3|\xb4\xc2\x9c\x00\x00AD\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>51</v>
+      </c>
+      <c r="G50" t="n">
+        <v>12</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:15</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1978891444</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-1393.56</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:14</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01NE\x95R\x07\xc2\xa0\x00\x00AL\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>51</v>
+      </c>
+      <c r="G51" t="n">
+        <v>12</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:18</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1167413767</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-1393.56</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:22</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01U\xfb\x81Bm\xc2\x98\x00\x00A\x18\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>51</v>
+      </c>
+      <c r="G52" t="n">
+        <v>12</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:25</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4219552365</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K52" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-1395.65</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01X\xf4\xd6*\x0c\xc2\x9a\x00\x00A\x18\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>51</v>
+      </c>
+      <c r="G53" t="n">
+        <v>12</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:28</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4107676172</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K53" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-1393.56</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:27</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01Z\x9c\xffo,\xc2\x9a\x00\x00A\x14\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>51</v>
+      </c>
+      <c r="G54" t="n">
+        <v>12</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:30</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2633985836</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K54" t="n">
+        <v>11</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-1393.56</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:29</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\\\x04\xdb\xbbr\xc2\x9a\x00\x00A(\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>51</v>
+      </c>
+      <c r="G55" t="n">
+        <v>12</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:32</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>81509234</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K55" t="n">
+        <v>11</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:31</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01^\xb78Mc\xc2\x98\x00\x00A\x10\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>51</v>
+      </c>
+      <c r="G56" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:34</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3073920355</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K56" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-1393.56</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:33</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01`\xd0d\x00\x9f\xc2\x9a\x00\x00A\x18\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>51</v>
+      </c>
+      <c r="G57" t="n">
+        <v>12</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:36</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3496214687</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K57" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-1393.56</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:35</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01bFtA\xc1\xc2\x9a\x00\x00A\x14\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>51</v>
+      </c>
+      <c r="G58" t="n">
+        <v>12</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:38</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1182024129</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K58" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:37</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01d\x9eZ?7\xc2\x9a\x00\x00A\x0c\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>51</v>
+      </c>
+      <c r="G59" t="n">
+        <v>12</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:40</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2656714551</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K59" t="n">
+        <v>11</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:39</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01f\xff\xa0}\r\xc2\x98\x00\x00A\x0c\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>51</v>
+      </c>
+      <c r="G60" t="n">
+        <v>12</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:42</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4288707853</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K60" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:41</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01i\x95\x1d\xd5\x83\xc2\x9a\x00\x00A\x14\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>51</v>
+      </c>
+      <c r="G61" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:45</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2501760387</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K61" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:44</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01k&gt;1@\x93\xc2\x98\x00\x00A\x18\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>51</v>
+      </c>
+      <c r="G62" t="n">
+        <v>12</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:47</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1043415187</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K62" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:46</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01m\x99aGL\xc2\x9a\x00\x00A\x1c\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>51</v>
+      </c>
+      <c r="G63" t="n">
+        <v>12</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:49</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2573289292</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K63" t="n">
+        <v>11</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:48</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01o\x99\xe7. \xc2\x9a\x00\x00A\x18\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>51</v>
+      </c>
+      <c r="G64" t="n">
+        <v>12</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:51</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2582064672</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K64" t="n">
+        <v>11</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01r\x1e\xcaO\xe4\xc2\x98\x00\x00A\x18\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>51</v>
+      </c>
+      <c r="G65" t="n">
+        <v>12</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:54</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>516575204</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:53</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01t=\xf6GL\xc2\x9a\x00\x00A\x14\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>51</v>
+      </c>
+      <c r="G66" t="n">
+        <v>12</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:56</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1039550284</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K66" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:55</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01wl\x07x\xab\xc2\x98\x00\x00A\x14\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>51</v>
+      </c>
+      <c r="G67" t="n">
+        <v>12</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:17:59</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1812428971</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K67" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:57</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01x\x8c\xf7\x0e\xf9\xc2\x98\x00\x00A\x18\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>51</v>
+      </c>
+      <c r="G68" t="n">
+        <v>12</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:18:00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2365001465</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K68" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:18:59</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01{\rT\xa0&gt;\xc2\x98\x00\x00A\x10\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>51</v>
+      </c>
+      <c r="G69" t="n">
+        <v>12</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:18:03</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>223649854</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K69" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:19:02</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01}\x03Z\xfdI\xc2\x98\x00\x00A\x14\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>51</v>
+      </c>
+      <c r="G70" t="n">
+        <v>12</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:18:05</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>56294729</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:19:04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x01\x7fU\xb0t\x1c\xc2\x9a\x00\x00A4\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>51</v>
+      </c>
+      <c r="G71" t="n">
+        <v>12</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:18:07</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1437627420</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>-69</v>
+      </c>
+      <c r="K71" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>histo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:28</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x00\x00\xe0\x01\x9c\xc2\x96\x00\x00A8\x00\x00D\xac\x9f0'</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>51</v>
+      </c>
+      <c r="G72" t="n">
+        <v>12</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:32</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>14680476</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K72" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-1385.17</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:31</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x02E%R\xb1\xc2\x98\x00\x00A\x1c\x00\x00D\xac\x9f0'</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>51</v>
+      </c>
+      <c r="G73" t="n">
+        <v>12</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:34</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1160073905</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K73" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-1385.17</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:33</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x04\xbc\x9euL\xc2\x96\x00\x00A8\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>51</v>
+      </c>
+      <c r="G74" t="n">
+        <v>12</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:36</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3164501324</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K74" t="n">
+        <v>13</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:35</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x06T\xf5B\x86\xc2\x94\x00\x00A(\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:38</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1425359494</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K75" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:37</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x08\x07\x9e 3\xc2\x96\x00\x00A4\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>51</v>
+      </c>
+      <c r="G76" t="n">
+        <v>12</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:40</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>127803443</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K76" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:38</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\ndPH\xde\xc2\x96\x00\x00A$\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>51</v>
+      </c>
+      <c r="G77" t="n">
+        <v>12</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:42</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1682983134</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K77" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:41</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x0c\x8f\x00\xdd\x10\xc2\x96\x00\x00A0\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>51</v>
+      </c>
+      <c r="G78" t="n">
+        <v>12</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:44</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2399198480</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:43</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x0f\xff\x1d\x9a\x1a\xc2\x96\x00\x00A0\x00\x00D\xad\xab\x9f'</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>51</v>
+      </c>
+      <c r="G79" t="n">
+        <v>12</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:47</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4280130074</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K79" t="n">
+        <v>13</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:46</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x11\xf8zch\xc2\x94\x00\x00A4\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>51</v>
+      </c>
+      <c r="G80" t="n">
+        <v>12</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:49</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4168770408</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K80" t="n">
+        <v>13</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:47</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x13v#\xa9&lt;\xc2\x96\x00\x00A0\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>51</v>
+      </c>
+      <c r="G81" t="n">
+        <v>12</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:51</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1982048572</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K81" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:50</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x15\xdc\x85P\x07\xc2\x98\x00\x00A,\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>51</v>
+      </c>
+      <c r="G82" t="n">
+        <v>12</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:24:53</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3699724295</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K82" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:25:59</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03\x1eq\xad\x97V\xc2\x98\x00\x00A4\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>51</v>
+      </c>
+      <c r="G83" t="n">
+        <v>12</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:02</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1907201878</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K83" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03 \xb3\xdfn\xd2\xc2\x96\x00\x00A,\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>51</v>
+      </c>
+      <c r="G84" t="n">
+        <v>12</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:04</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3017764562</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K84" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:03</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03#\\\x12\x907\xc2\x94\x00\x00A(\x00\x00D\xadh\x83'</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>51</v>
+      </c>
+      <c r="G85" t="n">
+        <v>12</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:07</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1544720439</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K85" t="n">
+        <v>13</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03%]\xfa\x19\x94\xc2\x96\x00\x00A8\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>51</v>
+      </c>
+      <c r="G86" t="n">
+        <v>12</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:09</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1576671636</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>-64</v>
+      </c>
+      <c r="K86" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:08</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>b"\x01U3\x0ch\xf0\x03'\xcb\n'\xde\xc2\x98\x00\x00A(\x00\x00D\xadh\x83"</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>51</v>
+      </c>
+      <c r="G87" t="n">
+        <v>12</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:11</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>3406440414</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K87" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-1391.46</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03)\x03\x8c\xdd=\xc2\x96\x00\x00A8\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>51</v>
+      </c>
+      <c r="G88" t="n">
+        <v>12</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:13</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>59563325</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K88" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:12</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03+\xf8t\x96O\xc2\x98\x00\x00A(\x00\x00D\xad%h'</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>51</v>
+      </c>
+      <c r="G89" t="n">
+        <v>12</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:15</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4168390223</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K89" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-1389.36</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:14</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03-\xba~(\x10\xc2\x94\x00\x00A4\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>51</v>
+      </c>
+      <c r="G90" t="n">
+        <v>12</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:17</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3128829968</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K90" t="n">
+        <v>13</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-10-15 22:26:16</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\x03/8\x14\xc1\xce\xc2\x96\x00\x00A0\x00\x00D\xac\xe2L'</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>51</v>
+      </c>
+      <c r="G91" t="n">
+        <v>12</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2025-10-15 20:25:19</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>940884430</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>-66</v>
+      </c>
+      <c r="K91" t="n">
+        <v>13</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-1387.27</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>histo2</t>
         </is>
       </c>
     </row>
@@ -1042,7 +5099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,13 +5129,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-111.5</v>
+        <v>-73</v>
       </c>
       <c r="C2" t="n">
-        <v>-10.5</v>
+        <v>13.5</v>
       </c>
       <c r="D2" t="n">
-        <v>282.0669555664062</v>
+        <v>1412.431884765625</v>
       </c>
     </row>
     <row r="3">
@@ -1086,13 +5143,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-111.5</v>
+        <v>-73</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.5</v>
+        <v>13.75</v>
       </c>
       <c r="D3" t="n">
-        <v>282.0669555664062</v>
+        <v>1412.431884765625</v>
       </c>
     </row>
     <row r="4">
@@ -1100,13 +5157,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-111.5</v>
+        <v>-74</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.5</v>
+        <v>13.75</v>
       </c>
       <c r="D4" t="n">
-        <v>282.0669555664062</v>
+        <v>1414.529052734375</v>
       </c>
     </row>
     <row r="5">
@@ -1114,13 +5171,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-111.5</v>
+        <v>-73</v>
       </c>
       <c r="C5" t="n">
-        <v>-10.5</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>282.0669555664062</v>
+        <v>1414.529052734375</v>
       </c>
     </row>
     <row r="6">
@@ -1128,13 +5185,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>-111.5</v>
+        <v>-74</v>
       </c>
       <c r="C6" t="n">
-        <v>-10.5</v>
+        <v>13.5</v>
       </c>
       <c r="D6" t="n">
-        <v>282.0669555664062</v>
+        <v>1414.529052734375</v>
       </c>
     </row>
     <row r="7">
@@ -1142,13 +5199,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-54</v>
+        <v>-73</v>
       </c>
       <c r="C7" t="n">
-        <v>10.25</v>
+        <v>13.75</v>
       </c>
       <c r="D7" t="n">
-        <v>-1852.833740234375</v>
+        <v>1414.529052734375</v>
       </c>
     </row>
     <row r="8">
@@ -1156,41 +5213,1175 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-54</v>
+        <v>-73</v>
       </c>
       <c r="C8" t="n">
-        <v>10.25</v>
+        <v>13.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1209.008178710938</v>
+        <v>1412.431884765625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-55</v>
+        <v>-73</v>
       </c>
       <c r="C9" t="n">
-        <v>10.75</v>
+        <v>13.5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1953.4970703125</v>
+        <v>1412.431884765625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-73</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1410.334716796875</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-73</v>
+      </c>
+      <c r="C11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1408.237548828125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-73</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1408.237548828125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1406.140380859375</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1408.237548828125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-72</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1406.140380859375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1406.140380859375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B17" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1406.140380859375</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-79</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1406.140380859375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1401.946166992188</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-79</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1404.043212890625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-78</v>
+      </c>
+      <c r="C21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1401.946166992188</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1399.848999023438</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1401.946166992188</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1404.043212890625</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1401.946166992188</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1401.946166992188</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1399.848999023438</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1399.848999023438</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1397.751831054688</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1397.751831054688</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1397.751831054688</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1395.654663085938</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1395.654663085938</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C34" t="n">
         <v>10.75</v>
       </c>
-      <c r="D10" t="n">
-        <v>-1940.914184570312</v>
+      <c r="D34" t="n">
+        <v>1395.654663085938</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C35" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1395.654663085938</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1395.654663085938</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C41" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>-78</v>
+      </c>
+      <c r="C43" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1395.654663085938</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C44" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C45" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C47" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1393.557495117188</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C48" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>-78</v>
+      </c>
+      <c r="C50" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C51" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C54" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C57" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C58" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C59" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C60" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C61" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C63" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C64" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C66" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C67" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C68" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C71" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C72" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1380.974609375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C73" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1380.974609375</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C74" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C75" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C76" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C77" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C78" t="n">
+        <v>11</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C79" t="n">
+        <v>11</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1389.363159179688</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C80" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C82" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C83" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C84" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C86" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C87" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1387.265991210938</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C88" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C89" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1385.1689453125</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C90" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C91" t="n">
+        <v>11</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1383.07177734375</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,58 +6441,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>b'\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B6" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B7" t="n">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/packets_export.xlsx
+++ b/packets_export.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5085,6 +5085,159 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>histo2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-10-16 09:08:55</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0cgt\x86\xdd\x9f\xa8\xa6\xe9\xc2\x84\x00\x00A\x14\x00\x00DYQ@'</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>51</v>
+      </c>
+      <c r="G92" t="n">
+        <v>12</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2025-01-01 00:05:49</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2678630121</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>-63</v>
+      </c>
+      <c r="K92" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-869.27</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>test_UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-10-16 09:13:03</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\xb6Z\xce\xf0\x0f\xf6\xc2\x90\x00\x00A\x14\x00\x00D\x9aE\x91'</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>51</v>
+      </c>
+      <c r="G93" t="n">
+        <v>12</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2025-10-16 09:09:46</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3471839222</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>-62</v>
+      </c>
+      <c r="K93" t="n">
+        <v>10</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-1236.27</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-10-16 09:13:29</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>b'\x01U3\x0ch\xf0\xb6s\xc1-\xff\xcd\xc2\x94\x00\x00A4\x00\x00D\x9aE\x91'</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>51</v>
+      </c>
+      <c r="G94" t="n">
+        <v>12</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2025-10-16 09:10:11</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3241017293</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>-76</v>
+      </c>
+      <c r="K94" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-1238.37</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>kk</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6382,6 +6535,48 @@
       </c>
       <c r="D91" t="n">
         <v>1383.07177734375</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>-66</v>
+      </c>
+      <c r="C92" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D92" t="n">
+        <v>869.26953125</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>-72</v>
+      </c>
+      <c r="C93" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1234.173950195312</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C94" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1234.173950195312</v>
       </c>
     </row>
   </sheetData>

--- a/packets_export.xlsx
+++ b/packets_export.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4728,516 +4728,6 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:03</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\x03#\\\x12\x907\xc2\x94\x00\x00A(\x00\x00D\xadh\x83'</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>51</v>
-      </c>
-      <c r="G85" t="n">
-        <v>12</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:07</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1544720439</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>-65</v>
-      </c>
-      <c r="K85" t="n">
-        <v>13</v>
-      </c>
-      <c r="L85" t="n">
-        <v>-1389.36</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:05</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\x03%]\xfa\x19\x94\xc2\x96\x00\x00A8\x00\x00D\xad%h'</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>51</v>
-      </c>
-      <c r="G86" t="n">
-        <v>12</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:09</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1576671636</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>-64</v>
-      </c>
-      <c r="K86" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="L86" t="n">
-        <v>-1389.36</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:08</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>b"\x01U3\x0ch\xf0\x03'\xcb\n'\xde\xc2\x98\x00\x00A(\x00\x00D\xadh\x83"</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>51</v>
-      </c>
-      <c r="G87" t="n">
-        <v>12</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:11</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>3406440414</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>-66</v>
-      </c>
-      <c r="K87" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L87" t="n">
-        <v>-1391.46</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:10</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\x03)\x03\x8c\xdd=\xc2\x96\x00\x00A8\x00\x00D\xac\xe2L'</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>51</v>
-      </c>
-      <c r="G88" t="n">
-        <v>12</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:13</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>59563325</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>-65</v>
-      </c>
-      <c r="K88" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="L88" t="n">
-        <v>-1387.27</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:12</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\x03+\xf8t\x96O\xc2\x98\x00\x00A(\x00\x00D\xad%h'</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>51</v>
-      </c>
-      <c r="G89" t="n">
-        <v>12</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:15</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>4168390223</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>-65</v>
-      </c>
-      <c r="K89" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="L89" t="n">
-        <v>-1389.36</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:14</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\x03-\xba~(\x10\xc2\x94\x00\x00A4\x00\x00D\xac\xe2L'</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>51</v>
-      </c>
-      <c r="G90" t="n">
-        <v>12</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:17</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3128829968</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>-66</v>
-      </c>
-      <c r="K90" t="n">
-        <v>13</v>
-      </c>
-      <c r="L90" t="n">
-        <v>-1387.27</v>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2025-10-15 22:26:16</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\x03/8\x14\xc1\xce\xc2\x96\x00\x00A0\x00\x00D\xac\xe2L'</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>51</v>
-      </c>
-      <c r="G91" t="n">
-        <v>12</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2025-10-15 20:25:19</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>940884430</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>-66</v>
-      </c>
-      <c r="K91" t="n">
-        <v>13</v>
-      </c>
-      <c r="L91" t="n">
-        <v>-1387.27</v>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>histo2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2025-10-16 09:08:55</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0cgt\x86\xdd\x9f\xa8\xa6\xe9\xc2\x84\x00\x00A\x14\x00\x00DYQ@'</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>51</v>
-      </c>
-      <c r="G92" t="n">
-        <v>12</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2025-01-01 00:05:49</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2678630121</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>-63</v>
-      </c>
-      <c r="K92" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="L92" t="n">
-        <v>-869.27</v>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>test_UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2025-10-16 09:13:03</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\xb6Z\xce\xf0\x0f\xf6\xc2\x90\x00\x00A\x14\x00\x00D\x9aE\x91'</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>51</v>
-      </c>
-      <c r="G93" t="n">
-        <v>12</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2025-10-16 09:09:46</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>3471839222</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>-62</v>
-      </c>
-      <c r="K93" t="n">
-        <v>10</v>
-      </c>
-      <c r="L93" t="n">
-        <v>-1236.27</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2025-10-16 09:13:29</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>b'\x01U3\x0ch\xf0\xb6s\xc1-\xff\xcd\xc2\x94\x00\x00A4\x00\x00D\x9aE\x91'</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>51</v>
-      </c>
-      <c r="G94" t="n">
-        <v>12</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2025-10-16 09:10:11</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>3241017293</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>-76</v>
-      </c>
-      <c r="K94" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="L94" t="n">
-        <v>-1238.37</v>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>kk</t>
         </is>
       </c>
     </row>
@@ -5252,7 +4742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6441,142 +5931,72 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B85" t="n">
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="C85" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>1387.265991210938</v>
+        <v>1383.07177734375</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B86" t="n">
-        <v>-75</v>
+        <v>-66</v>
       </c>
       <c r="C86" t="n">
-        <v>11.5</v>
+        <v>9.25</v>
       </c>
       <c r="D86" t="n">
-        <v>1385.1689453125</v>
+        <v>869.26953125</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B87" t="n">
-        <v>-76</v>
+        <v>-72</v>
       </c>
       <c r="C87" t="n">
-        <v>10.5</v>
+        <v>9.25</v>
       </c>
       <c r="D87" t="n">
-        <v>1387.265991210938</v>
+        <v>1234.173950195312</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B88" t="n">
-        <v>-75</v>
+        <v>-74</v>
       </c>
       <c r="C88" t="n">
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="D88" t="n">
-        <v>1383.07177734375</v>
+        <v>1234.173950195312</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B89" t="n">
-        <v>-76</v>
+        <v>-73</v>
       </c>
       <c r="C89" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="D89" t="n">
-        <v>1385.1689453125</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="n">
-        <v>-74</v>
-      </c>
-      <c r="C90" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D90" t="n">
-        <v>1383.07177734375</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="n">
-        <v>-75</v>
-      </c>
-      <c r="C91" t="n">
-        <v>11</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1383.07177734375</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="n">
-        <v>-66</v>
-      </c>
-      <c r="C92" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D92" t="n">
-        <v>869.26953125</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="n">
-        <v>-72</v>
-      </c>
-      <c r="C93" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D93" t="n">
-        <v>1234.173950195312</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="n">
-        <v>-74</v>
-      </c>
-      <c r="C94" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="D94" t="n">
-        <v>1234.173950195312</v>
+        <v>1167.065063476562</v>
       </c>
     </row>
   </sheetData>
